--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -10,13 +10,14 @@
     <sheet name="Weekly Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Category Aggregation" sheetId="2" r:id="rId2"/>
     <sheet name="Quantity Pivot" sheetId="3" r:id="rId3"/>
+    <sheet name="Sample Statistics" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>文件名称</t>
   </si>
@@ -85,6 +86,12 @@
   </si>
   <si>
     <t>汇总</t>
+  </si>
+  <si>
+    <t>总样品数</t>
+  </si>
+  <si>
+    <t>身体乳300ml单瓶</t>
   </si>
 </sst>
 </file>
@@ -622,4 +629,47 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,10 +43,16 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>All order-2026-02-27-10_34.csv</t>
-  </si>
-  <si>
-    <t>26/02/2026</t>
+    <t>03-02.csv</t>
+  </si>
+  <si>
+    <t>03-03.csv</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -58,6 +64,9 @@
     <t>销售额</t>
   </si>
   <si>
+    <t>汇率后(销售额)</t>
+  </si>
+  <si>
     <t>P列折后价</t>
   </si>
   <si>
@@ -68,9 +77,6 @@
   </si>
   <si>
     <t>寄样支出</t>
-  </si>
-  <si>
-    <t>汇率后(销售额)</t>
   </si>
   <si>
     <t>身体乳</t>
@@ -449,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -483,7 +489,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>95332</v>
@@ -502,6 +508,32 @@
       </c>
       <c r="H2">
         <v>75.08</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>95332</v>
+      </c>
+      <c r="D3">
+        <v>26.48</v>
+      </c>
+      <c r="E3">
+        <v>95332</v>
+      </c>
+      <c r="F3">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="G3">
+        <v>6.22</v>
+      </c>
+      <c r="H3">
+        <v>28.24</v>
       </c>
     </row>
   </sheetData>
@@ -511,67 +543,67 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>95332</v>
       </c>
       <c r="D2">
+        <v>26.48</v>
+      </c>
+      <c r="E2">
         <v>95332</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>9.359999999999999</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>6.22</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>46.84</v>
-      </c>
-      <c r="H2">
-        <v>26.48</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -586,10 +618,62 @@
         <v>0</v>
       </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>28.24</v>
       </c>
-      <c r="H3">
-        <v>0</v>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>95332</v>
+      </c>
+      <c r="D4">
+        <v>26.48</v>
+      </c>
+      <c r="E4">
+        <v>95332</v>
+      </c>
+      <c r="F4">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="G4">
+        <v>6.22</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>28.24</v>
       </c>
     </row>
   </sheetData>
@@ -599,30 +683,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
     </row>
@@ -633,23 +726,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -657,15 +753,21 @@
       <c r="C2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
     </row>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>文件名称</t>
   </si>
@@ -49,12 +49,18 @@
     <t>03-03.csv</t>
   </si>
   <si>
+    <t>0304.csv</t>
+  </si>
+  <si>
     <t>02/03/2026</t>
   </si>
   <si>
     <t>03/03/2026</t>
   </si>
   <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -89,6 +95,9 @@
   </si>
   <si>
     <t>身体乳单瓶</t>
+  </si>
+  <si>
+    <t>身体乳双瓶</t>
   </si>
   <si>
     <t>汇总</t>
@@ -455,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -489,7 +498,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>95332</v>
@@ -515,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>95332</v>
@@ -534,6 +543,32 @@
       </c>
       <c r="H3">
         <v>28.24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>247865</v>
+      </c>
+      <c r="D4">
+        <v>68.84999999999999</v>
+      </c>
+      <c r="E4">
+        <v>247865</v>
+      </c>
+      <c r="F4">
+        <v>28.08</v>
+      </c>
+      <c r="G4">
+        <v>15.75</v>
+      </c>
+      <c r="H4">
+        <v>75.08</v>
       </c>
     </row>
   </sheetData>
@@ -543,41 +578,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>95332</v>
@@ -600,10 +635,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -626,10 +661,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>95332</v>
@@ -652,10 +687,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -673,6 +708,58 @@
         <v>0</v>
       </c>
       <c r="H5">
+        <v>28.24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>247865</v>
+      </c>
+      <c r="D6">
+        <v>68.84999999999999</v>
+      </c>
+      <c r="E6">
+        <v>247865</v>
+      </c>
+      <c r="F6">
+        <v>28.08</v>
+      </c>
+      <c r="G6">
+        <v>15.75</v>
+      </c>
+      <c r="H6">
+        <v>46.84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>28.24</v>
       </c>
     </row>
@@ -683,23 +770,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -707,16 +797,36 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="C3">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
         <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -726,26 +836,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -754,12 +867,15 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -769,6 +885,9 @@
       </c>
       <c r="D3">
         <v>2</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,22 +43,28 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>03-02.csv</t>
-  </si>
-  <si>
-    <t>03-03.csv</t>
-  </si>
-  <si>
-    <t>0304.csv</t>
-  </si>
-  <si>
-    <t>02/03/2026</t>
-  </si>
-  <si>
-    <t>03/03/2026</t>
-  </si>
-  <si>
-    <t>04/03/2026</t>
+    <t>0308.csv</t>
+  </si>
+  <si>
+    <t>0309.csv</t>
+  </si>
+  <si>
+    <t>0310.csv</t>
+  </si>
+  <si>
+    <t>0311.csv</t>
+  </si>
+  <si>
+    <t>08/03/2026</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -94,19 +100,22 @@
     <t>商品名称</t>
   </si>
   <si>
+    <t>身体乳300ml单瓶</t>
+  </si>
+  <si>
     <t>身体乳单瓶</t>
   </si>
   <si>
     <t>身体乳双瓶</t>
   </si>
   <si>
+    <t>身体乳三瓶</t>
+  </si>
+  <si>
     <t>汇总</t>
   </si>
   <si>
     <t>总样品数</t>
-  </si>
-  <si>
-    <t>身体乳300ml单瓶</t>
   </si>
 </sst>
 </file>
@@ -464,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -498,25 +507,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>95332</v>
+        <v>149114</v>
       </c>
       <c r="D2">
-        <v>26.48</v>
+        <v>41.42</v>
       </c>
       <c r="E2">
-        <v>95332</v>
+        <v>149114</v>
       </c>
       <c r="F2">
-        <v>9.359999999999999</v>
+        <v>12.44</v>
       </c>
       <c r="G2">
-        <v>6.22</v>
+        <v>8.25</v>
       </c>
       <c r="H2">
-        <v>75.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -524,25 +533,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>95332</v>
+        <v>295531</v>
       </c>
       <c r="D3">
-        <v>26.48</v>
+        <v>82.09</v>
       </c>
       <c r="E3">
-        <v>95332</v>
+        <v>295531</v>
       </c>
       <c r="F3">
-        <v>9.359999999999999</v>
+        <v>37.44</v>
       </c>
       <c r="G3">
-        <v>6.22</v>
+        <v>19.32</v>
       </c>
       <c r="H3">
-        <v>28.24</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -550,25 +559,51 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>247865</v>
+        <v>152533</v>
       </c>
       <c r="D4">
-        <v>68.84999999999999</v>
+        <v>42.37</v>
       </c>
       <c r="E4">
-        <v>247865</v>
+        <v>152533</v>
       </c>
       <c r="F4">
-        <v>28.08</v>
+        <v>18.72</v>
       </c>
       <c r="G4">
-        <v>15.75</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H4">
-        <v>75.08</v>
+        <v>28.24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>202896</v>
+      </c>
+      <c r="D5">
+        <v>56.36</v>
+      </c>
+      <c r="E5">
+        <v>202896</v>
+      </c>
+      <c r="F5">
+        <v>15.52</v>
+      </c>
+      <c r="G5">
+        <v>10.28</v>
+      </c>
+      <c r="H5">
+        <v>51.66</v>
       </c>
     </row>
   </sheetData>
@@ -578,41 +613,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>95332</v>
@@ -630,136 +665,162 @@
         <v>6.22</v>
       </c>
       <c r="H2">
-        <v>46.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>53782</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>14.94</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>53782</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="H3">
-        <v>28.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>95332</v>
+        <v>295531</v>
       </c>
       <c r="D4">
-        <v>26.48</v>
+        <v>82.09</v>
       </c>
       <c r="E4">
-        <v>95332</v>
+        <v>295531</v>
       </c>
       <c r="F4">
-        <v>9.359999999999999</v>
+        <v>37.44</v>
       </c>
       <c r="G4">
-        <v>6.22</v>
+        <v>19.32</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>152533</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>42.37</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>152533</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>18.72</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H5">
-        <v>28.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>247865</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>68.84999999999999</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>247865</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>28.08</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>46.84</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>95332</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>26.48</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>95332</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="H7">
+        <v>23.42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>107564</v>
+      </c>
+      <c r="D8">
+        <v>29.88</v>
+      </c>
+      <c r="E8">
+        <v>107564</v>
+      </c>
+      <c r="F8">
+        <v>6.16</v>
+      </c>
+      <c r="G8">
+        <v>4.06</v>
+      </c>
+      <c r="H8">
         <v>28.24</v>
       </c>
     </row>
@@ -770,63 +831,109 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D4">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
         <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -841,27 +948,27 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -870,24 +977,24 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>2</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,28 +43,16 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>0308.csv</t>
-  </si>
-  <si>
-    <t>0309.csv</t>
-  </si>
-  <si>
-    <t>0310.csv</t>
-  </si>
-  <si>
-    <t>0311.csv</t>
+    <t>越南本土店-03038.csv</t>
+  </si>
+  <si>
+    <t>越南本土店-0315.csv</t>
   </si>
   <si>
     <t>08/03/2026</t>
   </si>
   <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>11/03/2026</t>
+    <t>14/03/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -101,6 +89,9 @@
   </si>
   <si>
     <t>身体乳300ml单瓶</t>
+  </si>
+  <si>
+    <t>身体乳300ml双瓶</t>
   </si>
   <si>
     <t>身体乳单瓶</t>
@@ -473,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -507,25 +498,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>149114</v>
+        <v>936027</v>
       </c>
       <c r="D2">
-        <v>41.42</v>
+        <v>260.01</v>
       </c>
       <c r="E2">
-        <v>149114</v>
+        <v>936027</v>
       </c>
       <c r="F2">
-        <v>12.44</v>
+        <v>77.84</v>
       </c>
       <c r="G2">
-        <v>8.25</v>
+        <v>48.74999999999999</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>281.72</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,77 +524,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>295531</v>
+        <v>843099</v>
       </c>
       <c r="D3">
-        <v>82.09</v>
+        <v>234.19</v>
       </c>
       <c r="E3">
-        <v>295531</v>
+        <v>843099</v>
       </c>
       <c r="F3">
-        <v>37.44</v>
+        <v>81.03999999999999</v>
       </c>
       <c r="G3">
-        <v>19.32</v>
+        <v>45.35</v>
       </c>
       <c r="H3">
-        <v>23.42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>152533</v>
-      </c>
-      <c r="D4">
-        <v>42.37</v>
-      </c>
-      <c r="E4">
-        <v>152533</v>
-      </c>
-      <c r="F4">
-        <v>18.72</v>
-      </c>
-      <c r="G4">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="H4">
-        <v>28.24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>202896</v>
-      </c>
-      <c r="D5">
-        <v>56.36</v>
-      </c>
-      <c r="E5">
-        <v>202896</v>
-      </c>
-      <c r="F5">
-        <v>15.52</v>
-      </c>
-      <c r="G5">
-        <v>10.28</v>
-      </c>
-      <c r="H5">
-        <v>51.66</v>
+        <v>244.18</v>
       </c>
     </row>
   </sheetData>
@@ -613,215 +552,137 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>95332</v>
+        <v>629193</v>
       </c>
       <c r="D2">
-        <v>26.48</v>
+        <v>174.78</v>
       </c>
       <c r="E2">
-        <v>95332</v>
+        <v>629193</v>
       </c>
       <c r="F2">
-        <v>9.359999999999999</v>
+        <v>65.52</v>
       </c>
       <c r="G2">
-        <v>6.22</v>
+        <v>40.63</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>140.52</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>53782</v>
+        <v>306834</v>
       </c>
       <c r="D3">
-        <v>14.94</v>
+        <v>85.23</v>
       </c>
       <c r="E3">
-        <v>53782</v>
+        <v>306834</v>
       </c>
       <c r="F3">
-        <v>3.08</v>
+        <v>12.32</v>
       </c>
       <c r="G3">
-        <v>2.03</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>141.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>295531</v>
+        <v>638728</v>
       </c>
       <c r="D4">
-        <v>82.09</v>
+        <v>177.42</v>
       </c>
       <c r="E4">
-        <v>295531</v>
+        <v>638728</v>
       </c>
       <c r="F4">
-        <v>37.44</v>
+        <v>74.88</v>
       </c>
       <c r="G4">
-        <v>19.32</v>
+        <v>41.29</v>
       </c>
       <c r="H4">
-        <v>23.42</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>152533</v>
+        <v>204371</v>
       </c>
       <c r="D5">
-        <v>42.37</v>
+        <v>56.77</v>
       </c>
       <c r="E5">
-        <v>152533</v>
+        <v>204371</v>
       </c>
       <c r="F5">
-        <v>18.72</v>
+        <v>6.16</v>
       </c>
       <c r="G5">
-        <v>9.529999999999999</v>
+        <v>4.06</v>
       </c>
       <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>28.24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>95332</v>
-      </c>
-      <c r="D7">
-        <v>26.48</v>
-      </c>
-      <c r="E7">
-        <v>95332</v>
-      </c>
-      <c r="F7">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="G7">
-        <v>6.22</v>
-      </c>
-      <c r="H7">
-        <v>23.42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>107564</v>
-      </c>
-      <c r="D8">
-        <v>29.88</v>
-      </c>
-      <c r="E8">
-        <v>107564</v>
-      </c>
-      <c r="F8">
-        <v>6.16</v>
-      </c>
-      <c r="G8">
-        <v>4.06</v>
-      </c>
-      <c r="H8">
-        <v>28.24</v>
+        <v>127.08</v>
       </c>
     </row>
   </sheetData>
@@ -831,46 +692,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -878,62 +727,49 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5">
         <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
       <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6">
-        <v>3</v>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -943,58 +779,49 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,16 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>越南本土店-03038.csv</t>
-  </si>
-  <si>
-    <t>越南本土店-0315.csv</t>
-  </si>
-  <si>
-    <t>08/03/2026</t>
-  </si>
-  <si>
-    <t>14/03/2026</t>
+    <t>0316.csv</t>
+  </si>
+  <si>
+    <t>0317.csv</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -91,22 +91,16 @@
     <t>身体乳300ml单瓶</t>
   </si>
   <si>
-    <t>身体乳300ml双瓶</t>
+    <t>身体乳三瓶</t>
+  </si>
+  <si>
+    <t>汇总</t>
+  </si>
+  <si>
+    <t>总样品数</t>
   </si>
   <si>
     <t>身体乳单瓶</t>
-  </si>
-  <si>
-    <t>身体乳双瓶</t>
-  </si>
-  <si>
-    <t>身体乳三瓶</t>
-  </si>
-  <si>
-    <t>汇总</t>
-  </si>
-  <si>
-    <t>总样品数</t>
   </si>
 </sst>
 </file>
@@ -501,22 +495,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>936027</v>
+        <v>361545</v>
       </c>
       <c r="D2">
-        <v>260.01</v>
+        <v>100.43</v>
       </c>
       <c r="E2">
-        <v>936027</v>
+        <v>336545</v>
       </c>
       <c r="F2">
-        <v>77.84</v>
+        <v>37.32</v>
       </c>
       <c r="G2">
-        <v>48.74999999999999</v>
+        <v>19.19</v>
       </c>
       <c r="H2">
-        <v>281.72</v>
+        <v>51.66</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -527,22 +521,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>843099</v>
+        <v>53782</v>
       </c>
       <c r="D3">
-        <v>234.19</v>
+        <v>14.94</v>
       </c>
       <c r="E3">
-        <v>843099</v>
+        <v>53782</v>
       </c>
       <c r="F3">
-        <v>81.03999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="G3">
-        <v>45.35</v>
+        <v>2.03</v>
       </c>
       <c r="H3">
-        <v>244.18</v>
+        <v>75.08</v>
       </c>
     </row>
   </sheetData>
@@ -589,22 +583,22 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>629193</v>
+        <v>200199</v>
       </c>
       <c r="D2">
-        <v>174.78</v>
+        <v>55.61</v>
       </c>
       <c r="E2">
-        <v>629193</v>
+        <v>200199</v>
       </c>
       <c r="F2">
-        <v>65.52</v>
+        <v>28.08</v>
       </c>
       <c r="G2">
-        <v>40.63</v>
+        <v>13.1</v>
       </c>
       <c r="H2">
-        <v>140.52</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -615,22 +609,22 @@
         <v>21</v>
       </c>
       <c r="C3">
-        <v>306834</v>
+        <v>161346</v>
       </c>
       <c r="D3">
-        <v>85.23</v>
+        <v>44.82</v>
       </c>
       <c r="E3">
-        <v>306834</v>
+        <v>136346</v>
       </c>
       <c r="F3">
-        <v>12.32</v>
+        <v>9.24</v>
       </c>
       <c r="G3">
-        <v>8.119999999999999</v>
+        <v>6.09</v>
       </c>
       <c r="H3">
-        <v>141.2</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -641,22 +635,22 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>638728</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>177.42</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>638728</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>74.88</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>41.29</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>117.1</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -667,22 +661,22 @@
         <v>21</v>
       </c>
       <c r="C5">
-        <v>204371</v>
+        <v>53782</v>
       </c>
       <c r="D5">
-        <v>56.77</v>
+        <v>14.94</v>
       </c>
       <c r="E5">
-        <v>204371</v>
+        <v>53782</v>
       </c>
       <c r="F5">
-        <v>6.16</v>
+        <v>3.08</v>
       </c>
       <c r="G5">
-        <v>4.06</v>
+        <v>2.03</v>
       </c>
       <c r="H5">
-        <v>127.08</v>
+        <v>28.24</v>
       </c>
     </row>
   </sheetData>
@@ -692,7 +686,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -711,10 +705,10 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -725,7 +719,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -733,43 +727,10 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5">
         <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -793,7 +754,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -801,27 +762,27 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,22 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>0316.csv</t>
-  </si>
-  <si>
-    <t>0317.csv</t>
-  </si>
-  <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
-    <t>17/03/2026</t>
+    <t>0329.csv</t>
+  </si>
+  <si>
+    <t>0330.csv</t>
+  </si>
+  <si>
+    <t>0331.csv</t>
+  </si>
+  <si>
+    <t>29/03/2026</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -91,16 +97,13 @@
     <t>身体乳300ml单瓶</t>
   </si>
   <si>
-    <t>身体乳三瓶</t>
+    <t>身体乳单瓶</t>
   </si>
   <si>
     <t>汇总</t>
   </si>
   <si>
     <t>总样品数</t>
-  </si>
-  <si>
-    <t>身体乳单瓶</t>
   </si>
 </sst>
 </file>
@@ -458,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -492,25 +495,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>361545</v>
+        <v>186900</v>
       </c>
       <c r="D2">
-        <v>100.43</v>
+        <v>51.92</v>
       </c>
       <c r="E2">
-        <v>336545</v>
+        <v>186900</v>
       </c>
       <c r="F2">
-        <v>37.32</v>
+        <v>28.08</v>
       </c>
       <c r="G2">
-        <v>19.19</v>
+        <v>18.66</v>
       </c>
       <c r="H2">
-        <v>51.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -518,25 +521,51 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>53782</v>
+        <v>365500</v>
       </c>
       <c r="D3">
-        <v>14.94</v>
+        <v>101.53</v>
       </c>
       <c r="E3">
-        <v>53782</v>
+        <v>365500</v>
       </c>
       <c r="F3">
-        <v>3.08</v>
+        <v>46.8</v>
       </c>
       <c r="G3">
-        <v>2.03</v>
+        <v>31.1</v>
       </c>
       <c r="H3">
-        <v>75.08</v>
+        <v>51.66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>487946</v>
+      </c>
+      <c r="D4">
+        <v>135.54</v>
+      </c>
+      <c r="E4">
+        <v>468334</v>
+      </c>
+      <c r="F4">
+        <v>46.68</v>
+      </c>
+      <c r="G4">
+        <v>30.97</v>
+      </c>
+      <c r="H4">
+        <v>51.66</v>
       </c>
     </row>
   </sheetData>
@@ -546,93 +575,93 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2">
-        <v>200199</v>
+        <v>186900</v>
       </c>
       <c r="D2">
-        <v>55.61</v>
+        <v>51.92</v>
       </c>
       <c r="E2">
-        <v>200199</v>
+        <v>186900</v>
       </c>
       <c r="F2">
         <v>28.08</v>
       </c>
       <c r="G2">
-        <v>13.1</v>
+        <v>18.66</v>
       </c>
       <c r="H2">
-        <v>23.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3">
-        <v>161346</v>
+        <v>365500</v>
       </c>
       <c r="D3">
-        <v>44.82</v>
+        <v>101.53</v>
       </c>
       <c r="E3">
-        <v>136346</v>
+        <v>365500</v>
       </c>
       <c r="F3">
-        <v>9.24</v>
+        <v>46.8</v>
       </c>
       <c r="G3">
-        <v>6.09</v>
+        <v>31.1</v>
       </c>
       <c r="H3">
-        <v>28.24</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -650,32 +679,58 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>46.84</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>53782</v>
+        <v>357200</v>
       </c>
       <c r="D5">
-        <v>14.94</v>
+        <v>99.22</v>
       </c>
       <c r="E5">
-        <v>53782</v>
+        <v>357200</v>
       </c>
       <c r="F5">
-        <v>3.08</v>
+        <v>37.44</v>
       </c>
       <c r="G5">
-        <v>2.03</v>
+        <v>24.88</v>
       </c>
       <c r="H5">
+        <v>23.42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>130746</v>
+      </c>
+      <c r="D6">
+        <v>36.32</v>
+      </c>
+      <c r="E6">
+        <v>111134</v>
+      </c>
+      <c r="F6">
+        <v>9.24</v>
+      </c>
+      <c r="G6">
+        <v>6.09</v>
+      </c>
+      <c r="H6">
         <v>28.24</v>
       </c>
     </row>
@@ -686,51 +741,63 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -745,21 +812,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -773,16 +840,16 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>2</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
   <si>
     <t>文件名称</t>
   </si>
@@ -52,6 +52,9 @@
     <t>0331.csv</t>
   </si>
   <si>
+    <t>0401.csv</t>
+  </si>
+  <si>
     <t>29/03/2026</t>
   </si>
   <si>
@@ -61,6 +64,9 @@
     <t>31/03/2026</t>
   </si>
   <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>身体乳300ml</t>
   </si>
   <si>
+    <t>防晒霜</t>
+  </si>
+  <si>
     <t>商品名称</t>
   </si>
   <si>
@@ -98,6 +107,12 @@
   </si>
   <si>
     <t>身体乳单瓶</t>
+  </si>
+  <si>
+    <t>身体乳双瓶</t>
+  </si>
+  <si>
+    <t>防晒霜单瓶</t>
   </si>
   <si>
     <t>汇总</t>
@@ -461,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -495,7 +510,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>186900</v>
@@ -521,7 +536,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>365500</v>
@@ -547,7 +562,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>487946</v>
@@ -565,6 +580,32 @@
         <v>30.97</v>
       </c>
       <c r="H4">
+        <v>51.66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>548015</v>
+      </c>
+      <c r="D5">
+        <v>152.23</v>
+      </c>
+      <c r="E5">
+        <v>533015</v>
+      </c>
+      <c r="F5">
+        <v>58.24999999999999</v>
+      </c>
+      <c r="G5">
+        <v>33.37</v>
+      </c>
+      <c r="H5">
         <v>51.66</v>
       </c>
     </row>
@@ -575,41 +616,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>186900</v>
@@ -632,10 +673,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>365500</v>
@@ -658,10 +699,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -684,10 +725,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>357200</v>
@@ -710,10 +751,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>130746</v>
@@ -732,6 +773,84 @@
       </c>
       <c r="H6">
         <v>28.24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>420433</v>
+      </c>
+      <c r="D7">
+        <v>116.79</v>
+      </c>
+      <c r="E7">
+        <v>405433</v>
+      </c>
+      <c r="F7">
+        <v>46.8</v>
+      </c>
+      <c r="G7">
+        <v>28.19</v>
+      </c>
+      <c r="H7">
+        <v>23.42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>43582</v>
+      </c>
+      <c r="D8">
+        <v>12.11</v>
+      </c>
+      <c r="E8">
+        <v>43582</v>
+      </c>
+      <c r="F8">
+        <v>3.08</v>
+      </c>
+      <c r="G8">
+        <v>2.03</v>
+      </c>
+      <c r="H8">
+        <v>28.24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9">
+        <v>84000</v>
+      </c>
+      <c r="D9">
+        <v>23.33</v>
+      </c>
+      <c r="E9">
+        <v>84000</v>
+      </c>
+      <c r="F9">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="G9">
+        <v>3.15</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -741,26 +860,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -771,10 +893,13 @@
       <c r="D2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -785,19 +910,59 @@
       <c r="D3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D4">
+      <c r="D6">
         <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -807,26 +972,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -835,12 +1003,15 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -849,7 +1020,10 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
   <si>
     <t>文件名称</t>
   </si>
@@ -55,6 +55,9 @@
     <t>0401.csv</t>
   </si>
   <si>
+    <t>0402.csv</t>
+  </si>
+  <si>
     <t>29/03/2026</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>01/04/2026</t>
   </si>
   <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -110,6 +116,9 @@
   </si>
   <si>
     <t>身体乳双瓶</t>
+  </si>
+  <si>
+    <t>身体乳三瓶</t>
   </si>
   <si>
     <t>防晒霜单瓶</t>
@@ -476,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -510,7 +519,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>186900</v>
@@ -536,7 +545,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>365500</v>
@@ -562,7 +571,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>487946</v>
@@ -588,7 +597,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>548015</v>
@@ -607,6 +616,32 @@
       </c>
       <c r="H5">
         <v>51.66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>1043013</v>
+      </c>
+      <c r="D6">
+        <v>289.73</v>
+      </c>
+      <c r="E6">
+        <v>1014277</v>
+      </c>
+      <c r="F6">
+        <v>124.76</v>
+      </c>
+      <c r="G6">
+        <v>68.86</v>
+      </c>
+      <c r="H6">
+        <v>75.08</v>
       </c>
     </row>
   </sheetData>
@@ -616,41 +651,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>186900</v>
@@ -673,10 +708,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>365500</v>
@@ -699,10 +734,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -725,10 +760,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>357200</v>
@@ -751,10 +786,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>130746</v>
@@ -777,10 +812,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>420433</v>
@@ -803,10 +838,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>43582</v>
@@ -829,10 +864,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>84000</v>
@@ -851,6 +886,58 @@
       </c>
       <c r="H9">
         <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10">
+        <v>999431</v>
+      </c>
+      <c r="D10">
+        <v>277.62</v>
+      </c>
+      <c r="E10">
+        <v>979411</v>
+      </c>
+      <c r="F10">
+        <v>121.68</v>
+      </c>
+      <c r="G10">
+        <v>66.83</v>
+      </c>
+      <c r="H10">
+        <v>46.84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11">
+        <v>43582</v>
+      </c>
+      <c r="D11">
+        <v>12.11</v>
+      </c>
+      <c r="E11">
+        <v>34866</v>
+      </c>
+      <c r="F11">
+        <v>3.08</v>
+      </c>
+      <c r="G11">
+        <v>2.03</v>
+      </c>
+      <c r="H11">
+        <v>28.24</v>
       </c>
     </row>
   </sheetData>
@@ -860,29 +947,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -896,10 +986,13 @@
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -913,10 +1006,13 @@
       <c r="E3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -930,10 +1026,13 @@
       <c r="E4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -945,24 +1044,50 @@
         <v>0</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6">
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>5</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>7</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>6</v>
+      </c>
+      <c r="F7">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -972,29 +1097,32 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -1006,12 +1134,15 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1023,7 +1154,10 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,34 +43,22 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>0329.csv</t>
-  </si>
-  <si>
-    <t>0330.csv</t>
-  </si>
-  <si>
-    <t>0331.csv</t>
-  </si>
-  <si>
-    <t>0401.csv</t>
-  </si>
-  <si>
-    <t>0402.csv</t>
-  </si>
-  <si>
-    <t>29/03/2026</t>
-  </si>
-  <si>
-    <t>30/03/2026</t>
-  </si>
-  <si>
-    <t>31/03/2026</t>
-  </si>
-  <si>
-    <t>01/04/2026</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
+    <t>0406.csv</t>
+  </si>
+  <si>
+    <t>0407.csv</t>
+  </si>
+  <si>
+    <t>0408.csv</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -103,9 +91,6 @@
     <t>身体乳300ml</t>
   </si>
   <si>
-    <t>防晒霜</t>
-  </si>
-  <si>
     <t>商品名称</t>
   </si>
   <si>
@@ -116,12 +101,6 @@
   </si>
   <si>
     <t>身体乳双瓶</t>
-  </si>
-  <si>
-    <t>身体乳三瓶</t>
-  </si>
-  <si>
-    <t>防晒霜单瓶</t>
   </si>
   <si>
     <t>汇总</t>
@@ -485,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -519,22 +498,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>186900</v>
+        <v>703712</v>
       </c>
       <c r="D2">
-        <v>51.92</v>
+        <v>195.48</v>
       </c>
       <c r="E2">
-        <v>186900</v>
+        <v>703712</v>
       </c>
       <c r="F2">
-        <v>28.08</v>
+        <v>71.67999999999999</v>
       </c>
       <c r="G2">
-        <v>18.66</v>
+        <v>41.78</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -545,25 +524,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>365500</v>
+        <v>642615</v>
       </c>
       <c r="D3">
-        <v>101.53</v>
+        <v>178.5</v>
       </c>
       <c r="E3">
-        <v>365500</v>
+        <v>642615</v>
       </c>
       <c r="F3">
-        <v>46.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G3">
-        <v>31.1</v>
+        <v>42.66</v>
       </c>
       <c r="H3">
-        <v>51.66</v>
+        <v>37.54</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -571,76 +550,24 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>487946</v>
+        <v>1043397</v>
       </c>
       <c r="D4">
-        <v>135.54</v>
+        <v>289.83</v>
       </c>
       <c r="E4">
-        <v>468334</v>
+        <v>1006606</v>
       </c>
       <c r="F4">
-        <v>46.68</v>
+        <v>109.12</v>
       </c>
       <c r="G4">
-        <v>30.97</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="H4">
-        <v>51.66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5">
-        <v>548015</v>
-      </c>
-      <c r="D5">
-        <v>152.23</v>
-      </c>
-      <c r="E5">
-        <v>533015</v>
-      </c>
-      <c r="F5">
-        <v>58.24999999999999</v>
-      </c>
-      <c r="G5">
-        <v>33.37</v>
-      </c>
-      <c r="H5">
-        <v>51.66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>1043013</v>
-      </c>
-      <c r="D6">
-        <v>289.73</v>
-      </c>
-      <c r="E6">
-        <v>1014277</v>
-      </c>
-      <c r="F6">
-        <v>124.76</v>
-      </c>
-      <c r="G6">
-        <v>68.86</v>
-      </c>
-      <c r="H6">
         <v>75.08</v>
       </c>
     </row>
@@ -651,56 +578,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C2">
-        <v>186900</v>
+        <v>572966</v>
       </c>
       <c r="D2">
-        <v>51.92</v>
+        <v>159.16</v>
       </c>
       <c r="E2">
-        <v>186900</v>
+        <v>572966</v>
       </c>
       <c r="F2">
-        <v>28.08</v>
+        <v>65.52</v>
       </c>
       <c r="G2">
-        <v>18.66</v>
+        <v>37.72</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -708,235 +635,131 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>365500</v>
+        <v>130746</v>
       </c>
       <c r="D3">
-        <v>101.53</v>
+        <v>36.32</v>
       </c>
       <c r="E3">
-        <v>365500</v>
+        <v>130746</v>
       </c>
       <c r="F3">
-        <v>46.8</v>
+        <v>6.16</v>
       </c>
       <c r="G3">
-        <v>31.1</v>
+        <v>4.06</v>
       </c>
       <c r="H3">
-        <v>23.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>599033</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>166.4</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>599033</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>65.52</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>40.63</v>
       </c>
       <c r="H4">
-        <v>28.24</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>357200</v>
+        <v>43582</v>
       </c>
       <c r="D5">
-        <v>99.22</v>
+        <v>12.11</v>
       </c>
       <c r="E5">
-        <v>357200</v>
+        <v>43582</v>
       </c>
       <c r="F5">
-        <v>37.44</v>
+        <v>3.08</v>
       </c>
       <c r="G5">
-        <v>24.88</v>
+        <v>2.03</v>
       </c>
       <c r="H5">
-        <v>23.42</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>130746</v>
+        <v>956233</v>
       </c>
       <c r="D6">
-        <v>36.32</v>
+        <v>265.62</v>
       </c>
       <c r="E6">
-        <v>111134</v>
+        <v>941233</v>
       </c>
       <c r="F6">
-        <v>9.24</v>
+        <v>102.96</v>
       </c>
       <c r="G6">
-        <v>6.09</v>
+        <v>65.50999999999999</v>
       </c>
       <c r="H6">
-        <v>28.24</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7">
-        <v>420433</v>
+        <v>87164</v>
       </c>
       <c r="D7">
-        <v>116.79</v>
+        <v>24.21</v>
       </c>
       <c r="E7">
-        <v>405433</v>
+        <v>65373</v>
       </c>
       <c r="F7">
-        <v>46.8</v>
+        <v>6.16</v>
       </c>
       <c r="G7">
-        <v>28.19</v>
+        <v>4.06</v>
       </c>
       <c r="H7">
-        <v>23.42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>43582</v>
-      </c>
-      <c r="D8">
-        <v>12.11</v>
-      </c>
-      <c r="E8">
-        <v>43582</v>
-      </c>
-      <c r="F8">
-        <v>3.08</v>
-      </c>
-      <c r="G8">
-        <v>2.03</v>
-      </c>
-      <c r="H8">
-        <v>28.24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9">
-        <v>84000</v>
-      </c>
-      <c r="D9">
-        <v>23.33</v>
-      </c>
-      <c r="E9">
-        <v>84000</v>
-      </c>
-      <c r="F9">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="G9">
-        <v>3.15</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10">
-        <v>999431</v>
-      </c>
-      <c r="D10">
-        <v>277.62</v>
-      </c>
-      <c r="E10">
-        <v>979411</v>
-      </c>
-      <c r="F10">
-        <v>121.68</v>
-      </c>
-      <c r="G10">
-        <v>66.83</v>
-      </c>
-      <c r="H10">
-        <v>46.84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11">
-        <v>43582</v>
-      </c>
-      <c r="D11">
-        <v>12.11</v>
-      </c>
-      <c r="E11">
-        <v>34866</v>
-      </c>
-      <c r="F11">
-        <v>3.08</v>
-      </c>
-      <c r="G11">
-        <v>2.03</v>
-      </c>
-      <c r="H11">
         <v>28.24</v>
       </c>
     </row>
@@ -947,52 +770,40 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -1001,93 +812,35 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1097,67 +850,49 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,22 +43,16 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>0406.csv</t>
-  </si>
-  <si>
-    <t>0407.csv</t>
-  </si>
-  <si>
-    <t>0408.csv</t>
-  </si>
-  <si>
-    <t>06/04/2026</t>
-  </si>
-  <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>08/04/2026</t>
+    <t>0503week.csv</t>
+  </si>
+  <si>
+    <t>0510week.csv</t>
+  </si>
+  <si>
+    <t>03/05/2026</t>
+  </si>
+  <si>
+    <t>10/05/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -97,10 +91,16 @@
     <t>身体乳300ml单瓶</t>
   </si>
   <si>
+    <t>身体乳300ml双瓶</t>
+  </si>
+  <si>
     <t>身体乳单瓶</t>
   </si>
   <si>
     <t>身体乳双瓶</t>
+  </si>
+  <si>
+    <t>身体乳三瓶</t>
   </si>
   <si>
     <t>汇总</t>
@@ -113,16 +113,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -138,7 +130,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -146,30 +138,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,32 +438,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -498,25 +472,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>703712</v>
+        <v>3760797</v>
       </c>
       <c r="D2">
-        <v>195.48</v>
+        <v>1044.67</v>
       </c>
       <c r="E2">
-        <v>703712</v>
+        <v>3546038</v>
       </c>
       <c r="F2">
-        <v>71.67999999999999</v>
+        <v>408.4</v>
       </c>
       <c r="G2">
-        <v>41.78</v>
+        <v>231.82</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>239.36</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -524,51 +498,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>642615</v>
+        <v>6724567</v>
       </c>
       <c r="D3">
-        <v>178.5</v>
+        <v>1867.94</v>
       </c>
       <c r="E3">
-        <v>642615</v>
+        <v>6399841</v>
       </c>
       <c r="F3">
-        <v>68.59999999999999</v>
+        <v>738.5999999999999</v>
       </c>
       <c r="G3">
-        <v>42.66</v>
+        <v>419.54</v>
       </c>
       <c r="H3">
-        <v>37.54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>1043397</v>
-      </c>
-      <c r="D4">
-        <v>289.83</v>
-      </c>
-      <c r="E4">
-        <v>1006606</v>
-      </c>
-      <c r="F4">
-        <v>109.12</v>
-      </c>
-      <c r="G4">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="H4">
-        <v>75.08</v>
+        <v>187.7</v>
       </c>
     </row>
   </sheetData>
@@ -578,189 +526,137 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" t="s">
         <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>572966</v>
+        <v>3218527</v>
       </c>
       <c r="D2">
-        <v>159.16</v>
+        <v>894.04</v>
       </c>
       <c r="E2">
-        <v>572966</v>
+        <v>3042737</v>
       </c>
       <c r="F2">
-        <v>65.52</v>
+        <v>383.76</v>
       </c>
       <c r="G2">
-        <v>37.72</v>
+        <v>215.58</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>140.52</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>130746</v>
+        <v>542270</v>
       </c>
       <c r="D3">
-        <v>36.32</v>
+        <v>150.63</v>
       </c>
       <c r="E3">
-        <v>130746</v>
+        <v>503301</v>
       </c>
       <c r="F3">
-        <v>6.16</v>
+        <v>24.64</v>
       </c>
       <c r="G3">
-        <v>4.06</v>
+        <v>16.24</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>98.83999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>599033</v>
+        <v>5668956</v>
       </c>
       <c r="D4">
-        <v>166.4</v>
+        <v>1574.71</v>
       </c>
       <c r="E4">
-        <v>599033</v>
+        <v>5428961</v>
       </c>
       <c r="F4">
-        <v>65.52</v>
+        <v>673.92</v>
       </c>
       <c r="G4">
-        <v>40.63</v>
+        <v>376.91</v>
       </c>
       <c r="H4">
-        <v>23.42</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>43582</v>
+        <v>1055611</v>
       </c>
       <c r="D5">
-        <v>12.11</v>
+        <v>293.23</v>
       </c>
       <c r="E5">
-        <v>43582</v>
+        <v>970880</v>
       </c>
       <c r="F5">
-        <v>3.08</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G5">
-        <v>2.03</v>
+        <v>42.63</v>
       </c>
       <c r="H5">
-        <v>14.12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>956233</v>
-      </c>
-      <c r="D6">
-        <v>265.62</v>
-      </c>
-      <c r="E6">
-        <v>941233</v>
-      </c>
-      <c r="F6">
-        <v>102.96</v>
-      </c>
-      <c r="G6">
-        <v>65.50999999999999</v>
-      </c>
-      <c r="H6">
-        <v>46.84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7">
-        <v>87164</v>
-      </c>
-      <c r="D7">
-        <v>24.21</v>
-      </c>
-      <c r="E7">
-        <v>65373</v>
-      </c>
-      <c r="F7">
-        <v>6.16</v>
-      </c>
-      <c r="G7">
-        <v>4.06</v>
-      </c>
-      <c r="H7">
-        <v>28.24</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -770,77 +666,84 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>28</v>
       </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
+      <c r="B7">
+        <v>37</v>
+      </c>
+      <c r="C7">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -854,45 +757,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>25</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="B3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowHeight="17400"/>
   </bookViews>
   <sheets>
     <sheet name="Weekly Summary" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,28 @@
     <sheet name="Quantity Pivot" sheetId="3" r:id="rId3"/>
     <sheet name="Sample Statistics" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Category Aggregation'!$A$1:$H$11</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +59,22 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>0503week.csv</t>
-  </si>
-  <si>
-    <t>0510week.csv</t>
-  </si>
-  <si>
-    <t>03/05/2026</t>
-  </si>
-  <si>
-    <t>10/05/2026</t>
+    <t>越南本土店-2月份.csv</t>
+  </si>
+  <si>
+    <t>28/02/2026</t>
+  </si>
+  <si>
+    <t>越南本土店-3月份.csv</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>越南本土店-4月份.csv</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -79,19 +101,22 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>未分类</t>
+  </si>
+  <si>
     <t>身体乳</t>
   </si>
   <si>
     <t>身体乳300ml</t>
   </si>
   <si>
+    <t>防晒霜</t>
+  </si>
+  <si>
     <t>商品名称</t>
   </si>
   <si>
     <t>身体乳300ml单瓶</t>
-  </si>
-  <si>
-    <t>身体乳300ml双瓶</t>
   </si>
   <si>
     <t>身体乳单瓶</t>
@@ -112,25 +137,368 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -138,18 +506,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -432,14 +1094,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
@@ -472,333 +1134,569 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>3760797</v>
+        <v>4050520</v>
       </c>
       <c r="D2">
-        <v>1044.67</v>
+        <v>1125.14</v>
       </c>
       <c r="E2">
-        <v>3546038</v>
+        <v>4009535</v>
       </c>
       <c r="F2">
-        <v>408.4</v>
+        <v>322.93</v>
       </c>
       <c r="G2">
-        <v>231.82</v>
+        <v>186.54</v>
       </c>
       <c r="H2">
-        <v>239.36</v>
+        <v>882.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3">
-        <v>6724567</v>
+        <v>11950278</v>
       </c>
       <c r="D3">
-        <v>1867.94</v>
+        <v>3319.52</v>
       </c>
       <c r="E3">
-        <v>6399841</v>
+        <v>11511591</v>
       </c>
       <c r="F3">
-        <v>738.5999999999999</v>
+        <v>1384.94</v>
       </c>
       <c r="G3">
-        <v>419.54</v>
+        <v>855.34</v>
       </c>
       <c r="H3">
-        <v>187.7</v>
+        <v>1201.96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>21846684</v>
+      </c>
+      <c r="D4">
+        <v>6068.52</v>
+      </c>
+      <c r="E4">
+        <v>20976710</v>
+      </c>
+      <c r="F4">
+        <v>2459.48</v>
+      </c>
+      <c r="G4">
+        <v>1409.26</v>
+      </c>
+      <c r="H4">
+        <v>1149.96</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="12.0769230769231" customWidth="1"/>
+    <col min="2" max="2" width="13.8461538461538" customWidth="1"/>
+    <col min="9" max="9" width="12.9230769230769"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" hidden="1" spans="1:9">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>119999</v>
+      </c>
+      <c r="D2">
+        <v>33.33</v>
+      </c>
+      <c r="E2">
+        <v>119999</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>2424622</v>
+      </c>
+      <c r="D3">
+        <v>673.51</v>
+      </c>
+      <c r="E3">
+        <v>2424622</v>
+      </c>
+      <c r="F3">
+        <v>271.44</v>
+      </c>
+      <c r="G3">
+        <v>154.97</v>
+      </c>
+      <c r="H3">
+        <v>444.98</v>
+      </c>
+      <c r="I3">
+        <f>C3/34</f>
+        <v>71312.4117647059</v>
+      </c>
+    </row>
+    <row r="4" hidden="1" spans="1:9">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1421899</v>
+      </c>
+      <c r="D4">
+        <v>394.97</v>
+      </c>
+      <c r="E4">
+        <v>1380914</v>
+      </c>
+      <c r="F4">
+        <v>43.12</v>
+      </c>
+      <c r="G4">
+        <v>28.42</v>
+      </c>
+      <c r="H4">
+        <v>437.72</v>
+      </c>
+    </row>
+    <row r="5" hidden="1" spans="1:9">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>84000</v>
+      </c>
+      <c r="D5">
+        <v>23.33</v>
+      </c>
+      <c r="E5">
+        <v>84000</v>
+      </c>
+      <c r="F5">
+        <v>8.37</v>
+      </c>
+      <c r="G5">
+        <v>3.15</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>9703143</v>
+      </c>
+      <c r="D6">
+        <v>2695.32</v>
+      </c>
+      <c r="E6">
+        <v>9472128</v>
+      </c>
+      <c r="F6">
+        <v>1254.24</v>
+      </c>
+      <c r="G6">
+        <v>773.93</v>
+      </c>
+      <c r="H6">
+        <v>608.92</v>
+      </c>
+      <c r="I6">
+        <f>C6/150</f>
+        <v>64687.62</v>
+      </c>
+    </row>
+    <row r="7" hidden="1" spans="1:9">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>2079135</v>
+      </c>
+      <c r="D7">
+        <v>577.54</v>
+      </c>
+      <c r="E7">
+        <v>1871463</v>
+      </c>
+      <c r="F7">
+        <v>113.96</v>
+      </c>
+      <c r="G7">
+        <v>75.11</v>
+      </c>
+      <c r="H7">
+        <v>593.04</v>
+      </c>
+    </row>
+    <row r="8" hidden="1" spans="1:9">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>168000</v>
+      </c>
+      <c r="D8">
+        <v>46.67</v>
+      </c>
+      <c r="E8">
+        <v>168000</v>
+      </c>
+      <c r="F8">
+        <v>16.74</v>
+      </c>
+      <c r="G8">
+        <v>6.3</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2">
-        <v>3218527</v>
-      </c>
-      <c r="D2">
-        <v>894.04</v>
-      </c>
-      <c r="E2">
-        <v>3042737</v>
-      </c>
-      <c r="F2">
-        <v>383.76</v>
-      </c>
-      <c r="G2">
-        <v>215.58</v>
-      </c>
-      <c r="H2">
-        <v>140.52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3">
-        <v>542270</v>
-      </c>
-      <c r="D3">
-        <v>150.63</v>
-      </c>
-      <c r="E3">
-        <v>503301</v>
-      </c>
-      <c r="F3">
-        <v>24.64</v>
-      </c>
-      <c r="G3">
-        <v>16.24</v>
-      </c>
-      <c r="H3">
-        <v>98.83999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <v>5668956</v>
-      </c>
-      <c r="D4">
-        <v>1574.71</v>
-      </c>
-      <c r="E4">
-        <v>5428961</v>
-      </c>
-      <c r="F4">
-        <v>673.92</v>
-      </c>
-      <c r="G4">
-        <v>376.91</v>
-      </c>
-      <c r="H4">
-        <v>117.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5">
-        <v>1055611</v>
-      </c>
-      <c r="D5">
-        <v>293.23</v>
-      </c>
-      <c r="E5">
-        <v>970880</v>
-      </c>
-      <c r="F5">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="G5">
-        <v>42.63</v>
-      </c>
-      <c r="H5">
-        <v>70.59999999999999</v>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9">
+        <v>19791700</v>
+      </c>
+      <c r="D9">
+        <v>5497.69</v>
+      </c>
+      <c r="E9">
+        <v>19120428</v>
+      </c>
+      <c r="F9">
+        <v>2321.28</v>
+      </c>
+      <c r="G9">
+        <v>1327.64</v>
+      </c>
+      <c r="H9">
+        <v>655.76</v>
+      </c>
+      <c r="I9">
+        <f>C9/206</f>
+        <v>96076.213592233</v>
+      </c>
+    </row>
+    <row r="10" hidden="1" spans="1:9">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>1718984</v>
+      </c>
+      <c r="D10">
+        <v>477.5</v>
+      </c>
+      <c r="E10">
+        <v>1520282</v>
+      </c>
+      <c r="F10">
+        <v>104.72</v>
+      </c>
+      <c r="G10">
+        <v>69.02</v>
+      </c>
+      <c r="H10">
+        <v>494.2</v>
+      </c>
+    </row>
+    <row r="11" hidden="1" spans="1:9">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>336000</v>
+      </c>
+      <c r="D11">
+        <v>93.33</v>
+      </c>
+      <c r="E11">
+        <v>336000</v>
+      </c>
+      <c r="F11">
+        <v>33.48</v>
+      </c>
+      <c r="G11">
+        <v>12.6</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H11" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="身体乳"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.6923076923077" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>37</v>
+      </c>
+      <c r="D2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>98</v>
+      </c>
+      <c r="D3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
         <v>24</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
-        <v>18</v>
-      </c>
-      <c r="C4">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <f>SUM(B2:B5)</f>
+        <v>34</v>
       </c>
       <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7">
-        <v>37</v>
-      </c>
-      <c r="C7">
-        <v>69</v>
+        <f>SUM(C2:C5)</f>
+        <v>150</v>
+      </c>
+      <c r="D6">
+        <f>SUM(D2:D5)</f>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>35</v>
+      </c>
+      <c r="E2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>28</v>
+      </c>
+      <c r="E3">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_local.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17400"/>
+    <workbookView windowWidth="28800" windowHeight="12460"/>
   </bookViews>
   <sheets>
     <sheet name="Weekly Summary" sheetId="1" r:id="rId1"/>
@@ -12,9 +12,6 @@
     <sheet name="Quantity Pivot" sheetId="3" r:id="rId3"/>
     <sheet name="Sample Statistics" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Category Aggregation'!$A$1:$H$11</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="38">
   <si>
     <t>文件名称</t>
   </si>
@@ -77,6 +74,12 @@
     <t>30/04/2026</t>
   </si>
   <si>
+    <t>越南本土-5月份.csv</t>
+  </si>
+  <si>
+    <t>31/05/2026</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -119,6 +122,9 @@
     <t>身体乳300ml单瓶</t>
   </si>
   <si>
+    <t>身体乳300ml双瓶</t>
+  </si>
+  <si>
     <t>身体乳单瓶</t>
   </si>
   <si>
@@ -126,6 +132,12 @@
   </si>
   <si>
     <t>身体乳三瓶</t>
+  </si>
+  <si>
+    <t>防晒霜单瓶</t>
+  </si>
+  <si>
+    <t>新产品(待核实)</t>
   </si>
   <si>
     <t>汇总</t>
@@ -144,10 +156,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -304,7 +323,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -313,6 +332,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -498,12 +523,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F2329"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F2329"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F2329"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F2329"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -607,70 +647,67 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -685,75 +722,85 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1100,10 +1147,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="3" max="3" width="12.9230769230769"/>
+    <col min="5" max="5" width="9.30769230769231"/>
+    <col min="6" max="6" width="14.0769230769231"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1129,7 +1181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1140,7 +1192,7 @@
         <v>4050520</v>
       </c>
       <c r="D2">
-        <v>1125.14</v>
+        <v>1043.14</v>
       </c>
       <c r="E2">
         <v>4009535</v>
@@ -1154,8 +1206,11 @@
       <c r="H2">
         <v>882.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="J2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1166,7 +1221,7 @@
         <v>11950278</v>
       </c>
       <c r="D3">
-        <v>3319.52</v>
+        <v>3077.59</v>
       </c>
       <c r="E3">
         <v>11511591</v>
@@ -1180,8 +1235,11 @@
       <c r="H3">
         <v>1201.96</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="J3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1192,7 +1250,7 @@
         <v>21846684</v>
       </c>
       <c r="D4">
-        <v>6068.52</v>
+        <v>5626.24</v>
       </c>
       <c r="E4">
         <v>20976710</v>
@@ -1205,6 +1263,90 @@
       </c>
       <c r="H4">
         <v>1149.96</v>
+      </c>
+      <c r="J4">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>18906879</v>
+      </c>
+      <c r="D5">
+        <v>4869.14</v>
+      </c>
+      <c r="E5">
+        <v>18181021</v>
+      </c>
+      <c r="F5">
+        <v>2018.49</v>
+      </c>
+      <c r="G5">
+        <v>1151.12</v>
+      </c>
+      <c r="H5">
+        <v>1031.84</v>
+      </c>
+      <c r="J5">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="C6">
+        <f>C2/J2</f>
+        <v>98793.1707317073</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-692.3</v>
+      </c>
+      <c r="F6">
+        <f>E6/J2</f>
+        <v>-16.8853658536585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="C7">
+        <f>C3/J3</f>
+        <v>77098.5677419355</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-2603.29</v>
+      </c>
+      <c r="F7">
+        <f>E7/J3</f>
+        <v>-16.7954193548387</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="C8">
+        <f>C4/J4</f>
+        <v>103050.396226415</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-3407.23</v>
+      </c>
+      <c r="F8">
+        <f>E8/J4</f>
+        <v>-16.0718396226415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="C9">
+        <f>C5/J5</f>
+        <v>98988.8952879581</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-2341.14</v>
+      </c>
+      <c r="F9">
+        <f>E9/J5</f>
+        <v>-12.257277486911</v>
       </c>
     </row>
   </sheetData>
@@ -1215,53 +1357,48 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
-  <cols>
-    <col min="1" max="1" width="12.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="13.8461538461538" customWidth="1"/>
-    <col min="9" max="9" width="12.9230769230769"/>
-  </cols>
+  <sheetPr/>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" hidden="1" spans="1:9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>119999</v>
       </c>
       <c r="D2">
-        <v>33.33</v>
+        <v>30.9</v>
       </c>
       <c r="E2">
         <v>119999</v>
@@ -1276,18 +1413,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>2424622</v>
       </c>
       <c r="D3">
-        <v>673.51</v>
+        <v>624.42</v>
       </c>
       <c r="E3">
         <v>2424622</v>
@@ -1301,23 +1438,19 @@
       <c r="H3">
         <v>444.98</v>
       </c>
-      <c r="I3">
-        <f>C3/34</f>
-        <v>71312.4117647059</v>
-      </c>
-    </row>
-    <row r="4" hidden="1" spans="1:9">
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>1421899</v>
       </c>
       <c r="D4">
-        <v>394.97</v>
+        <v>366.19</v>
       </c>
       <c r="E4">
         <v>1380914</v>
@@ -1332,18 +1465,18 @@
         <v>437.72</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:9">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>84000</v>
       </c>
       <c r="D5">
-        <v>23.33</v>
+        <v>21.63</v>
       </c>
       <c r="E5">
         <v>84000</v>
@@ -1358,18 +1491,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>9703143</v>
       </c>
       <c r="D6">
-        <v>2695.32</v>
+        <v>2498.88</v>
       </c>
       <c r="E6">
         <v>9472128</v>
@@ -1383,23 +1516,19 @@
       <c r="H6">
         <v>608.92</v>
       </c>
-      <c r="I6">
-        <f>C6/150</f>
-        <v>64687.62</v>
-      </c>
-    </row>
-    <row r="7" hidden="1" spans="1:9">
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>2079135</v>
       </c>
       <c r="D7">
-        <v>577.54</v>
+        <v>535.45</v>
       </c>
       <c r="E7">
         <v>1871463</v>
@@ -1414,18 +1543,18 @@
         <v>593.04</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:9">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>168000</v>
       </c>
       <c r="D8">
-        <v>46.67</v>
+        <v>43.27</v>
       </c>
       <c r="E8">
         <v>168000</v>
@@ -1440,18 +1569,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>19791700</v>
       </c>
       <c r="D9">
-        <v>5497.69</v>
+        <v>5097.01</v>
       </c>
       <c r="E9">
         <v>19120428</v>
@@ -1465,23 +1594,19 @@
       <c r="H9">
         <v>655.76</v>
       </c>
-      <c r="I9">
-        <f>C9/206</f>
-        <v>96076.213592233</v>
-      </c>
-    </row>
-    <row r="10" hidden="1" spans="1:9">
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>1718984</v>
       </c>
       <c r="D10">
-        <v>477.5</v>
+        <v>442.69</v>
       </c>
       <c r="E10">
         <v>1520282</v>
@@ -1496,18 +1621,18 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:9">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>336000</v>
       </c>
       <c r="D11">
-        <v>93.33</v>
+        <v>86.53</v>
       </c>
       <c r="E11">
         <v>336000</v>
@@ -1522,15 +1647,85 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>15917538</v>
+      </c>
+      <c r="D12">
+        <v>4099.29</v>
+      </c>
+      <c r="E12">
+        <v>15380289</v>
+      </c>
+      <c r="F12">
+        <v>1834.56</v>
+      </c>
+      <c r="G12">
+        <v>1032.26</v>
+      </c>
+      <c r="H12">
+        <v>749.44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13">
+        <v>2905341</v>
+      </c>
+      <c r="D13">
+        <v>748.22</v>
+      </c>
+      <c r="E13">
+        <v>2716732</v>
+      </c>
+      <c r="F13">
+        <v>175.56</v>
+      </c>
+      <c r="G13">
+        <v>115.71</v>
+      </c>
+      <c r="H13">
+        <v>282.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14">
+        <v>84000</v>
+      </c>
+      <c r="D14">
+        <v>21.63</v>
+      </c>
+      <c r="E14">
+        <v>84000</v>
+      </c>
+      <c r="F14">
+        <v>8.37</v>
+      </c>
+      <c r="G14">
+        <v>3.15</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H11" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="身体乳"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -1539,15 +1734,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="18.6923076923077" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>9</v>
@@ -1558,10 +1750,13 @@
       <c r="D1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>14</v>
@@ -1572,64 +1767,127 @@
       <c r="D2">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
         <v>14</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>98</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>120</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
         <v>6</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6">
-        <f>SUM(B2:B5)</f>
+      <c r="E6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
         <v>34</v>
       </c>
-      <c r="C6">
-        <f>SUM(C2:C5)</f>
-        <v>150</v>
-      </c>
-      <c r="D6">
-        <f>SUM(D2:D5)</f>
-        <v>206</v>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9">
+        <v>41</v>
+      </c>
+      <c r="C9">
+        <v>155</v>
+      </c>
+      <c r="D9">
+        <v>212</v>
+      </c>
+      <c r="E9">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -1641,12 +1899,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="4"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>9</v>
@@ -1658,12 +1916,15 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>31</v>
@@ -1675,12 +1936,15 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>19</v>
@@ -1692,7 +1956,10 @@
         <v>28</v>
       </c>
       <c r="E3">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="F3">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
